--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484814_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484814_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P. FAYE</t>
+          <t>E. MORATA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.8252</v>
+        <v>8.910500000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>3.399</v>
+        <v>5.9626</v>
       </c>
       <c r="F2" t="n">
-        <v>4.4262</v>
+        <v>2.9479</v>
       </c>
       <c r="G2" t="n">
-        <v>2.544</v>
+        <v>6.5277</v>
       </c>
       <c r="H2" t="n">
-        <v>2.1216</v>
+        <v>0.5854</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4223</v>
+        <v>5.9423</v>
       </c>
       <c r="J2" t="n">
-        <v>1.3052</v>
+        <v>6.2969</v>
       </c>
       <c r="K2" t="n">
-        <v>1.0995</v>
+        <v>0.5713</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2057</v>
+        <v>5.7256</v>
       </c>
       <c r="M2" t="n">
-        <v>1.2388</v>
+        <v>0.2308</v>
       </c>
       <c r="N2" t="n">
-        <v>1.0221</v>
+        <v>0.0141</v>
       </c>
       <c r="O2" t="n">
         <v>0.2167</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9435</v>
+        <v>0.5661</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9435</v>
+        <v>2.4531</v>
       </c>
       <c r="S2" t="n">
-        <v>4.3378</v>
+        <v>0.5715</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0938</v>
+        <v>0.3075</v>
       </c>
       <c r="U2" t="n">
-        <v>2.2439</v>
+        <v>0.264</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. MORATA</t>
+          <t>P. FAYE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.4831</v>
+        <v>5.9716</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7732</v>
+        <v>2.4448</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7098</v>
+        <v>3.5268</v>
       </c>
       <c r="G3" t="n">
-        <v>6.5277</v>
+        <v>2.544</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5854</v>
+        <v>2.1216</v>
       </c>
       <c r="I3" t="n">
-        <v>5.9423</v>
+        <v>0.4223</v>
       </c>
       <c r="J3" t="n">
-        <v>6.2969</v>
+        <v>1.3052</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5713</v>
+        <v>1.0995</v>
       </c>
       <c r="L3" t="n">
-        <v>5.7256</v>
+        <v>0.2057</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2308</v>
+        <v>1.2388</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0141</v>
+        <v>1.0221</v>
       </c>
       <c r="O3" t="n">
         <v>0.2167</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5661</v>
+        <v>0.9435</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4531</v>
+        <v>0.9435</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8559</v>
+        <v>2.4841</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8818</v>
+        <v>1.1396</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0259</v>
+        <v>1.3445</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.7608</v>
+        <v>4.9855</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5892</v>
+        <v>2.999</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1717</v>
+        <v>1.9865</v>
       </c>
       <c r="G4" t="n">
         <v>4.4408</v>
@@ -766,13 +766,13 @@
         <v>0.5661</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0182</v>
+        <v>1.2429</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0617</v>
+        <v>0.4716</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9565</v>
+        <v>0.7713</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3208</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. CERVANTES GUERRA</t>
+          <t>A. FONT FENOLLAR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.9812</v>
+        <v>4.7702</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3886</v>
+        <v>0.6844</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5926</v>
+        <v>4.0858</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8411</v>
+        <v>1.2234</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5552</v>
+        <v>2.1177</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2859</v>
+        <v>-0.8943</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8745</v>
+        <v>-0.665</v>
       </c>
       <c r="K5" t="n">
-        <v>2.1341</v>
+        <v>1.2255</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7403</v>
+        <v>-1.8905</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0334</v>
+        <v>1.8884</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4211</v>
+        <v>0.8922</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4544</v>
+        <v>0.9962</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1322</v>
+        <v>0.5661</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0757</v>
+        <v>1.5096</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0459</v>
+        <v>1.113</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5044</v>
+        <v>0.4251</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5503</v>
+        <v>0.6879</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.038</v>
+        <v>1.8678</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.038</v>
+        <v>1.8678</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. LUENGO MATEO</t>
+          <t>L. CERVANTES GUERRA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.6459</v>
+        <v>4.1349</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0326</v>
+        <v>1.701</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6133</v>
+        <v>2.4339</v>
       </c>
       <c r="G6" t="n">
-        <v>2.3884</v>
+        <v>2.8411</v>
       </c>
       <c r="H6" t="n">
-        <v>2.9582</v>
+        <v>2.5552</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5698</v>
+        <v>0.2859</v>
       </c>
       <c r="J6" t="n">
-        <v>2.059</v>
+        <v>2.8745</v>
       </c>
       <c r="K6" t="n">
-        <v>2.7156</v>
+        <v>2.1341</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6566</v>
+        <v>0.7403</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3294</v>
+        <v>-0.0334</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2426</v>
+        <v>0.4211</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0868</v>
+        <v>-0.4544</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.1322</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9435</v>
+        <v>2.0757</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0123</v>
+        <v>0.1996</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3281</v>
+        <v>-0.192</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3404</v>
+        <v>0.3916</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2452</v>
+        <v>-0.038</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2452</v>
+        <v>-0.038</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. FONT FENOLLAR</t>
+          <t>P. LUENGO MATEO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.4016</v>
+        <v>4.1255</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4461</v>
+        <v>2.2476</v>
       </c>
       <c r="F7" t="n">
-        <v>3.8477</v>
+        <v>1.8778</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2234</v>
+        <v>2.3884</v>
       </c>
       <c r="H7" t="n">
-        <v>2.1177</v>
+        <v>2.9582</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8943</v>
+        <v>-0.5698</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.665</v>
+        <v>2.059</v>
       </c>
       <c r="K7" t="n">
-        <v>1.2255</v>
+        <v>2.7156</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.8905</v>
+        <v>-0.6566</v>
       </c>
       <c r="M7" t="n">
-        <v>1.8884</v>
+        <v>0.3294</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8922</v>
+        <v>0.2426</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9962</v>
+        <v>0.0868</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5661</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5096</v>
+        <v>0.9435</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2557</v>
+        <v>0.4919</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7055</v>
+        <v>-0.113</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4498</v>
+        <v>0.6049</v>
       </c>
       <c r="V7" t="n">
-        <v>1.8678</v>
+        <v>1.2452</v>
       </c>
       <c r="W7" t="n">
-        <v>1.8678</v>
+        <v>1.2452</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3.0446</v>
+        <v>2.6691</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8219</v>
+        <v>0.3935</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2227</v>
+        <v>2.2756</v>
       </c>
       <c r="G8" t="n">
         <v>0.5607</v>
@@ -1078,13 +1078,13 @@
         <v>2.2644</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8612</v>
+        <v>0.4857</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5349</v>
+        <v>0.1065</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3263</v>
+        <v>0.3792</v>
       </c>
       <c r="V8" t="n">
         <v>0.3018</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O. CASTRILLON RODRIGUEZ</t>
+          <t>P. ANTICH MINGUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6909</v>
+        <v>0.2509</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2433</v>
+        <v>-2.1872</v>
       </c>
       <c r="F10" t="n">
-        <v>2.9341</v>
+        <v>2.4381</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.3523</v>
+        <v>1.3555</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.1296</v>
+        <v>2.1349</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2227</v>
+        <v>-0.7795</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.5729</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.6963</v>
+        <v>1.1942</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1234</v>
+        <v>-1.1261</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2205</v>
+        <v>1.2873</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5666</v>
+        <v>0.9407</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3461</v>
+        <v>0.3466</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1322</v>
+        <v>-2.0757</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9435</v>
+        <v>-2.8305</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0757</v>
+        <v>0.7548</v>
       </c>
       <c r="S10" t="n">
-        <v>2.911</v>
+        <v>1.273</v>
       </c>
       <c r="T10" t="n">
-        <v>2.2731</v>
+        <v>0.5752</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6379</v>
+        <v>0.6978</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. ANTICH MINGUEZ</t>
+          <t>O. CASTRILLON RODRIGUEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1479</v>
+        <v>-0.5536</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1099</v>
+        <v>-3.5671</v>
       </c>
       <c r="F11" t="n">
-        <v>1.962</v>
+        <v>3.0135</v>
       </c>
       <c r="G11" t="n">
-        <v>1.3555</v>
+        <v>-3.3523</v>
       </c>
       <c r="H11" t="n">
-        <v>2.1349</v>
+        <v>-3.1296</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7795</v>
+        <v>-0.2227</v>
       </c>
       <c r="J11" t="n">
-        <v>0.06809999999999999</v>
+        <v>-3.5729</v>
       </c>
       <c r="K11" t="n">
-        <v>1.1942</v>
+        <v>-3.6963</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.1261</v>
+        <v>0.1234</v>
       </c>
       <c r="M11" t="n">
-        <v>1.2873</v>
+        <v>0.2205</v>
       </c>
       <c r="N11" t="n">
-        <v>0.9407</v>
+        <v>0.5666</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3466</v>
+        <v>-0.3461</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.0757</v>
+        <v>1.1322</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.8305</v>
+        <v>-0.9435</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7548</v>
+        <v>2.0757</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8741</v>
+        <v>1.6665</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6525</v>
+        <v>0.9493</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2217</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.3875</v>
+        <v>-1.7911</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0097</v>
+        <v>-2.3075</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6222</v>
+        <v>0.5164</v>
       </c>
       <c r="G12" t="n">
         <v>-0.2381</v>
@@ -1390,13 +1390,13 @@
         <v>2.4531</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2251</v>
+        <v>0.3712</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7396</v>
+        <v>-0.0374</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5144</v>
+        <v>0.4086</v>
       </c>
       <c r="V12" t="n">
         <v>-2.4904</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>33.2318</v>
+        <v>34.4074</v>
       </c>
       <c r="E13" t="n">
-        <v>8.1294</v>
+        <v>9.304999999999996</v>
       </c>
       <c r="F13" t="n">
         <v>25.1023</v>
@@ -1444,7 +1444,7 @@
         <v>12.7127</v>
       </c>
       <c r="K13" t="n">
-        <v>8.709999999999999</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="L13" t="n">
         <v>4.0026</v>
@@ -1468,16 +1468,16 @@
         <v>16.0395</v>
       </c>
       <c r="S13" t="n">
-        <v>8.723800000000001</v>
+        <v>9.8994</v>
       </c>
       <c r="T13" t="n">
-        <v>2.456599999999999</v>
+        <v>3.6324</v>
       </c>
       <c r="U13" t="n">
-        <v>6.267100000000001</v>
+        <v>6.267</v>
       </c>
       <c r="V13" t="n">
-        <v>1.508999999999999</v>
+        <v>1.509</v>
       </c>
       <c r="W13" t="n">
         <v>5.2256</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.0205</v>
+        <v>-0.7942</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.0007</v>
+        <v>-0.611</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0198</v>
+        <v>-0.1833</v>
       </c>
       <c r="G14" t="n">
         <v>0.5246</v>
@@ -1546,13 +1546,13 @@
         <v>1.5096</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.4884</v>
+        <v>-1.2621</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.5285</v>
+        <v>-1.1387</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0401</v>
+        <v>-0.1234</v>
       </c>
       <c r="V14" t="n">
         <v>1.2642</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>N. FELIZ CAMEAU</t>
+          <t>F. AJAYI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.9714</v>
+        <v>-1.7932</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.3532</v>
+        <v>-1.6179</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6183</v>
+        <v>-0.1753</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.0409</v>
+        <v>-1.8617</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.6667999999999999</v>
+        <v>-2.2038</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3742</v>
+        <v>0.3421</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9373</v>
+        <v>-0.4791</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8139</v>
+        <v>-1.1457</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1234</v>
+        <v>0.6666</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.9782</v>
+        <v>-1.3826</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.4806</v>
+        <v>-1.058</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4976</v>
+        <v>-0.3245</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.5661</v>
+        <v>1.6983</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.0757</v>
+        <v>-0.1887</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5096</v>
+        <v>1.887</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2392</v>
+        <v>-1.328</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7853</v>
+        <v>-0.95</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5461</v>
+        <v>-0.3779</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6036</v>
+        <v>-0.3018</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6036</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.2929</v>
+        <v>-2.1329</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.4332</v>
+        <v>-2.1409</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1402</v>
+        <v>0.008</v>
       </c>
       <c r="G16" t="n">
         <v>-1.0502</v>
@@ -1702,13 +1702,13 @@
         <v>0.1887</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1346</v>
+        <v>0.2947</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2939</v>
+        <v>-0.0016</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4286</v>
+        <v>0.2963</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6226</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. AJAYI</t>
+          <t>N. FELIZ CAMEAU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.4739</v>
+        <v>-2.4659</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.0076</v>
+        <v>-1.4249</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4663</v>
+        <v>-1.041</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.8617</v>
+        <v>-1.0409</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.2038</v>
+        <v>-0.6667999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3421</v>
+        <v>-0.3742</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4791</v>
+        <v>0.9373</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.1457</v>
+        <v>0.8139</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6666</v>
+        <v>0.1234</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3826</v>
+        <v>-1.9782</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.058</v>
+        <v>-1.4806</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3245</v>
+        <v>-0.4976</v>
       </c>
       <c r="P17" t="n">
-        <v>1.6983</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1887</v>
+        <v>-2.0757</v>
       </c>
       <c r="R17" t="n">
-        <v>1.887</v>
+        <v>1.5096</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.0087</v>
+        <v>-0.2553</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3398</v>
+        <v>-0.2865</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6689000000000001</v>
+        <v>0.0312</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3018</v>
+        <v>-0.6036</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3018</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.6114</v>
+        <v>-2.6378</v>
       </c>
       <c r="E18" t="n">
         <v>-0.3835</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.2279</v>
+        <v>-2.2543</v>
       </c>
       <c r="G18" t="n">
         <v>-1.5203</v>
@@ -1858,13 +1858,13 @@
         <v>0.9435</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9023</v>
+        <v>-0.9288</v>
       </c>
       <c r="T18" t="n">
         <v>-0.5291</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3733</v>
+        <v>-0.3997</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.7902</v>
+        <v>-3.0741</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4118</v>
+        <v>0.022</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.2019</v>
+        <v>-3.0961</v>
       </c>
       <c r="G19" t="n">
         <v>-1.4761</v>
@@ -1936,13 +1936,13 @@
         <v>0.1887</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2575</v>
+        <v>-0.5414</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0029</v>
+        <v>-0.3868</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2604</v>
+        <v>-0.1546</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2452</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. DOMINGUEZ TORRES</t>
+          <t>O. TALENS ALBERO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.3199</v>
+        <v>-4.2149</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.4244</v>
+        <v>-4.4814</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1046</v>
+        <v>0.2665</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.475</v>
+        <v>-5.5708</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.211</v>
+        <v>-3.6939</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.264</v>
+        <v>-1.8769</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.9135</v>
+        <v>-4.7133</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.4285</v>
+        <v>-3.4638</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.485</v>
+        <v>-1.2495</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5615</v>
+        <v>-0.8575</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7826</v>
+        <v>-0.23</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7789</v>
+        <v>-0.6274999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5661</v>
+        <v>1.887</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5096</v>
+        <v>1.887</v>
       </c>
       <c r="S20" t="n">
-        <v>0.589</v>
+        <v>-2.0781</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4325</v>
+        <v>-1.3151</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1565</v>
+        <v>-0.763</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.547</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.547</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O. TALENS ALBERO</t>
+          <t>P. TORMO HERRERO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.9967</v>
+        <v>-4.3727</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.8711</v>
+        <v>-4.4358</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1256</v>
+        <v>0.0631</v>
       </c>
       <c r="G21" t="n">
-        <v>-5.5708</v>
+        <v>-1.4268</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.6939</v>
+        <v>-0.8569</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.8769</v>
+        <v>-0.5698</v>
       </c>
       <c r="J21" t="n">
-        <v>-4.7133</v>
+        <v>-0.8781</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.4638</v>
+        <v>-0.2215</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2495</v>
+        <v>-0.6566</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8575</v>
+        <v>-0.5487</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.23</v>
+        <v>-0.6354</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6274999999999999</v>
+        <v>0.0868</v>
       </c>
       <c r="P21" t="n">
-        <v>1.887</v>
+        <v>-2.2644</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-3.0192</v>
       </c>
       <c r="R21" t="n">
-        <v>1.887</v>
+        <v>0.7548</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.8599</v>
+        <v>-0.3798</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.7048</v>
+        <v>-0.5385</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.1551</v>
+        <v>0.1588</v>
       </c>
       <c r="V21" t="n">
-        <v>1.547</v>
+        <v>-0.3018</v>
       </c>
       <c r="W21" t="n">
-        <v>1.547</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. TORMO HERRERO</t>
+          <t>J. DOMINGUEZ TORRES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.2604</v>
+        <v>-4.5106</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.8256</v>
+        <v>-4.3988</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4348</v>
+        <v>-0.1118</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.4268</v>
+        <v>-4.475</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8569</v>
+        <v>-3.211</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5698</v>
+        <v>-1.264</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.8781</v>
+        <v>-2.9135</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.2215</v>
+        <v>-2.4285</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6566</v>
+        <v>-0.485</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5487</v>
+        <v>-1.5615</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6354</v>
+        <v>-0.7826</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0868</v>
+        <v>-0.7789</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.2644</v>
+        <v>0.5661</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.0192</v>
+        <v>-0.9435</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7548</v>
+        <v>1.5096</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2674</v>
+        <v>-0.6017</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9283</v>
+        <v>-0.5417999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3391</v>
+        <v>-0.0599</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.4945</v>
+        <v>-5.9363</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.2148</v>
+        <v>-5.6302</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2797</v>
+        <v>-0.3062</v>
       </c>
       <c r="G23" t="n">
         <v>-1.3277</v>
@@ -2248,13 +2248,13 @@
         <v>1.887</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9023</v>
+        <v>-0.3442</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1634</v>
+        <v>-0.5788</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2611</v>
+        <v>0.2346</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2452</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-33.2318</v>
+        <v>-31.9326</v>
       </c>
       <c r="E24" t="n">
-        <v>-25.1023</v>
+        <v>-25.1024</v>
       </c>
       <c r="F24" t="n">
-        <v>-8.1295</v>
+        <v>-6.830399999999999</v>
       </c>
       <c r="G24" t="n">
         <v>-19.2249</v>
@@ -2299,10 +2299,10 @@
         <v>-5.4122</v>
       </c>
       <c r="J24" t="n">
-        <v>-6.5122</v>
+        <v>-6.512199999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>-5.1028</v>
+        <v>-5.102799999999999</v>
       </c>
       <c r="L24" t="n">
         <v>-1.4096</v>
@@ -2326,13 +2326,13 @@
         <v>12.2655</v>
       </c>
       <c r="S24" t="n">
-        <v>-8.723700000000001</v>
+        <v>-7.4247</v>
       </c>
       <c r="T24" t="n">
-        <v>-6.2671</v>
+        <v>-6.266900000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.4566</v>
+        <v>-1.1576</v>
       </c>
       <c r="V24" t="n">
         <v>-1.509</v>
